--- a/public/Data.xlsx
+++ b/public/Data.xlsx
@@ -19,61 +19,709 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="232">
   <si>
     <t>Key_word</t>
   </si>
   <si>
-    <t>Link_google_map</t>
-  </si>
-  <si>
-    <t>Aloha Nails - St.Mary''s | St.Vital - Nail Salon</t>
-  </si>
-  <si>
-    <t>NAIL TALK &amp; SPA (950W Peachtree)</t>
-  </si>
-  <si>
-    <t>Nails So Dep MC</t>
-  </si>
-  <si>
     <t>Danah beauty&amp;spa,beauty center,saloon</t>
   </si>
   <si>
-    <t>Monica''s Nails</t>
-  </si>
-  <si>
-    <t>Pandora''s Nail Salon</t>
-  </si>
-  <si>
-    <t>Sueann''s Nails &amp; spa</t>
-  </si>
-  <si>
-    <t>https://www.google.com/maps/place/Monica%27s+Nails/data=!4m7!3m6!1s0x88f4f94bf6ec6ca3:0x2e182567e38dc657!8m2!3d33.5748266!4d-84.3378624!16s%2Fg%2F1td5gz9j!19sChIJo2zs9kv59IgRV8aN42clGC4?authuser=0&amp;hl=en&amp;rclk=1</t>
-  </si>
-  <si>
-    <t>https://www.google.com/maps/place/Aloha+Nails+-+St.Mary%27s+%7C+St.Vital+-+Nail+Salon/data=!4m7!3m6!1s0x52ea766c2938f099:0x9fe8e3df641cd00a!8m2!3d49.8259648!4d-97.1154036!16s%2Fg%2F1v5_92d3!19sChIJmfA4KWx26lIRCtAcZN_j6J8?authuser=0&amp;hl=en&amp;rclk=1</t>
-  </si>
-  <si>
-    <t>https://www.google.com/maps/place/NAIL+TALK+%26+SPA+%28950W+Peachtree%29/data=!4m7!3m6!1s0x88f5046789bd327d:0x233226d689019d8a!8m2!3d33.7805316!4d-84.3884165!16s%2Fg%2F1hc0s9f3t!19sChIJfTK9iWcE9YgRip0BidYmMiM?authuser=0&amp;hl=en&amp;rclk=1</t>
-  </si>
-  <si>
-    <t>https://www.google.com/maps/place/Nails+So+Dep+MC/data=!4m7!3m6!1s0x88fe5be5b4a8c9cb:0x42eb0f760cef65d7!8m2!3d33.2073843!4d-79.9849563!16s%2Fg%2F11ghpn7lfr!19sChIJy8motOVb_ogR12XvDHYP60I?authuser=0&amp;hl=en&amp;rclk=1</t>
-  </si>
-  <si>
-    <t>https://www.google.com/maps/place/Danah+beauty%26spa,beauty+center,saloon/data=!4m7!3m6!1s0x151b5fb85d7981af:0x6ad59da137631903!8m2!3d31.9778171!4d35.8440452!16s%2Fg%2F12hqgb24l!19sChIJr4F5XbhfGxURAxljN6Gd1Wo?authuser=0&amp;hl=en&amp;rclk=1</t>
-  </si>
-  <si>
-    <t>https://www.google.com/maps/place/Pandora%27s+Nail+Salon/data=!4m7!3m6!1s0x88d9ab7ffa631a31:0x995316d56a049c6c!8m2!3d25.9884313!4d-80.1422826!16s%2Fg%2F1tk_kj1t!19sChIJMRpj-n-r2YgRbJwEatUWU5k?authuser=0&amp;hl=en&amp;rclk=1</t>
-  </si>
-  <si>
-    <t>https://www.google.com/maps/place/Sueann%27s+Nails+%26+spa/data=!4m7!3m6!1s0x89003f600f54da45:0x83ae61f336210155!8m2!3d33.612846!4d-78.9826146!16s%2Fg%2F1tcwr_j4!19sChIJRdpUD2A_AIkRVQEhNvNhroM?authuser=0&amp;hl=en&amp;rclk=1</t>
+    <t>Jolly Nails Spa</t>
+  </si>
+  <si>
+    <t>Karinas Nails</t>
+  </si>
+  <si>
+    <t>LA SPA &amp; NAILBAR</t>
+  </si>
+  <si>
+    <t>ProfessioNAIL QueensPlaza</t>
+  </si>
+  <si>
+    <t>Fancy Nails &amp; Spa Benton</t>
+  </si>
+  <si>
+    <t>TLC NAILS &amp; SPA Easley</t>
+  </si>
+  <si>
+    <t>VIP Nails and Spa</t>
+  </si>
+  <si>
+    <t>Verona Nails &amp; Spa</t>
+  </si>
+  <si>
+    <t>Secrets Nails &amp; Spa</t>
+  </si>
+  <si>
+    <t>Nailshop</t>
+  </si>
+  <si>
+    <t>Envogue Nails</t>
+  </si>
+  <si>
+    <t>Vip Nails Baytown</t>
+  </si>
+  <si>
+    <t>LUX Nails &amp; Lashes</t>
+  </si>
+  <si>
+    <t>Bedazzled nails and bar</t>
+  </si>
+  <si>
+    <t>GLORY NAILS &amp; BEAUTY II</t>
+  </si>
+  <si>
+    <t>Jolly Nails &amp; Spa</t>
+  </si>
+  <si>
+    <t>Prince Beauty Supply</t>
+  </si>
+  <si>
+    <t>Fontainebleau Nail Salon &amp; Spa</t>
+  </si>
+  <si>
+    <t>Maruti Eyebrow Threading and Lashes</t>
+  </si>
+  <si>
+    <t>LUXURY NAIL BAR (20% OFF SECONDS SERVICE FOR NEW CUSTOMERS) Monday to Wednesday. Please let Counter know!</t>
+  </si>
+  <si>
+    <t>Saige Boutique and Salon</t>
+  </si>
+  <si>
+    <t>Nails &amp; Spa Salon Midtown, NYC</t>
+  </si>
+  <si>
+    <t>Nail Talk &amp; Tan</t>
+  </si>
+  <si>
+    <t>Vienna Nail And lashes</t>
+  </si>
+  <si>
+    <t>Hollywood spa &amp; nails</t>
+  </si>
+  <si>
+    <t>Eric &amp; Mia Nails Spa (10% OFF New customers)</t>
+  </si>
+  <si>
+    <t>The White Spa Nails</t>
+  </si>
+  <si>
+    <t>360 Nails &amp; Spa</t>
+  </si>
+  <si>
+    <t>PALACE NAIL LOUNGE - MESA</t>
+  </si>
+  <si>
+    <t>Manhattan Beauty Supply</t>
+  </si>
+  <si>
+    <t>Le Passion Nails &amp; Spa</t>
+  </si>
+  <si>
+    <t>Vuvuzela Nail Spa</t>
+  </si>
+  <si>
+    <t>Joe Nails Salon Round Rock Austin Texas</t>
+  </si>
+  <si>
+    <t>Anna Nail and Spa</t>
+  </si>
+  <si>
+    <t>Professional Nails &amp; spa LLC</t>
+  </si>
+  <si>
+    <t>D’or Nail Bar &amp; Lash Atlanta</t>
+  </si>
+  <si>
+    <t>Tomato Nails Salon Inc</t>
+  </si>
+  <si>
+    <t>NAILS OF AMERICA LOOP 336 CONROE</t>
+  </si>
+  <si>
+    <t>Legacy Nail Salon</t>
+  </si>
+  <si>
+    <t>Magic Nails &amp; Tanning</t>
+  </si>
+  <si>
+    <t>Senorita nail &amp; spa</t>
+  </si>
+  <si>
+    <t>MV Nail Bar and Spa</t>
+  </si>
+  <si>
+    <t>Super Nail</t>
+  </si>
+  <si>
+    <t>Morii Nails Spa</t>
+  </si>
+  <si>
+    <t>Best Beauty Nail Salon</t>
+  </si>
+  <si>
+    <t>UPSCALE NAILS &amp; SPA | BEST NAIL DESIGNS IN STL | PERMANENT JEWELRY</t>
+  </si>
+  <si>
+    <t>Jenny''s Nails On The Drive</t>
+  </si>
+  <si>
+    <t>A Q Nails</t>
+  </si>
+  <si>
+    <t>Nails of America Baytown</t>
+  </si>
+  <si>
+    <t>Casa Blanca Nail Bar</t>
+  </si>
+  <si>
+    <t>DREAM NAIL SPA-Tidwell Rd,77044</t>
+  </si>
+  <si>
+    <t>A+ Nail Spa</t>
+  </si>
+  <si>
+    <t>LUSH NAIL BAR DUNWOODY (NEXT TO ONELIFE FITNESS/ OLD NAVY/ MARSHALL)</t>
+  </si>
+  <si>
+    <t>Lisa''s Nails And Spas</t>
+  </si>
+  <si>
+    <t>Q-Nails Summerwood</t>
+  </si>
+  <si>
+    <t>Nails Escape</t>
+  </si>
+  <si>
+    <t>LaBelle Spa &amp; Nails</t>
+  </si>
+  <si>
+    <t>Layla''s Day Spa 30% OFF 2nd SERVICES</t>
+  </si>
+  <si>
+    <t>Q''s Nails 2</t>
+  </si>
+  <si>
+    <t>Layla''s Day Spa (20% OFF NEW MANAGEMENT)</t>
+  </si>
+  <si>
+    <t>Edana Beauty ( Nail bar &amp; massage )</t>
+  </si>
+  <si>
+    <t>Omega Nails</t>
+  </si>
+  <si>
+    <t>M &amp; M nails and Spa</t>
+  </si>
+  <si>
+    <t>West Bend Nails</t>
+  </si>
+  <si>
+    <t>Trina Nails Of The World</t>
+  </si>
+  <si>
+    <t>Hector Nails</t>
+  </si>
+  <si>
+    <t>T and D Nail Salon</t>
+  </si>
+  <si>
+    <t>Jana Nails and Spa</t>
+  </si>
+  <si>
+    <t>Viva Nails, Hair &amp; Spa</t>
+  </si>
+  <si>
+    <t>Lacey Nails</t>
+  </si>
+  <si>
+    <t>K-Nails &amp; Spa</t>
+  </si>
+  <si>
+    <t>Rico Nails</t>
+  </si>
+  <si>
+    <t>XO Beauty Nails and Hair</t>
+  </si>
+  <si>
+    <t>Caribbean Nails &amp; Spa 84045</t>
+  </si>
+  <si>
+    <t>Luminous V Nail Spa - Springboro</t>
+  </si>
+  <si>
+    <t>Hot Tips Nail Lounge A1 of Rockaway</t>
+  </si>
+  <si>
+    <t>ATNL Nails - Spa &amp; Beauty</t>
+  </si>
+  <si>
+    <t>LA Nails in Lititz PA</t>
+  </si>
+  <si>
+    <t>Ooh La La Salon &amp; Spa</t>
+  </si>
+  <si>
+    <t>Top Prestige Nails</t>
+  </si>
+  <si>
+    <t>K1 Nails &amp; Spa</t>
+  </si>
+  <si>
+    <t>Craze Nails &amp; Spa in Lake Mary</t>
+  </si>
+  <si>
+    <t>Splendid Nail Bar</t>
+  </si>
+  <si>
+    <t>Sara’s Wax &amp; Beauty Bar</t>
+  </si>
+  <si>
+    <t>Key West Nail Lounge</t>
+  </si>
+  <si>
+    <t>Katie's Nails &amp; Spa</t>
+  </si>
+  <si>
+    <t>CHÍC NAIL LOUNGE BIGFORK</t>
+  </si>
+  <si>
+    <t>Images Face &amp; Body Clinic</t>
+  </si>
+  <si>
+    <t>Best Nail Lounge ( ShopRite Plaza On Lincoln &amp; East Landis Ave )</t>
+  </si>
+  <si>
+    <t>Wooster Nail Spa</t>
+  </si>
+  <si>
+    <t>Tommy Nails</t>
+  </si>
+  <si>
+    <t>West U Nails &amp; Facial</t>
+  </si>
+  <si>
+    <t>Millenia Nails &amp; Day Spa</t>
+  </si>
+  <si>
+    <t>Fancy Nail</t>
+  </si>
+  <si>
+    <t>Five Star Nail Salon</t>
+  </si>
+  <si>
+    <t>Midtown Centre Oriental Nails</t>
+  </si>
+  <si>
+    <t>Vy''s Nail Spa</t>
+  </si>
+  <si>
+    <t>Magic Nails of Lemont</t>
+  </si>
+  <si>
+    <t>Blissful Nail Lounge</t>
+  </si>
+  <si>
+    <t>Jasmine Nails Puyallup</t>
+  </si>
+  <si>
+    <t>Plano Nail Bar</t>
+  </si>
+  <si>
+    <t>RUBY’S NAILS SALON</t>
+  </si>
+  <si>
+    <t>Lux Nail Spa &amp; Hair Salon</t>
+  </si>
+  <si>
+    <t>Galaxy Nail Lounge</t>
+  </si>
+  <si>
+    <t>Urbane Nails &amp; Spa 2</t>
+  </si>
+  <si>
+    <t>Talk Nail &amp; Spa</t>
+  </si>
+  <si>
+    <t>3 sis nail</t>
+  </si>
+  <si>
+    <t>Avi Nail Spa Lash &amp; Brow</t>
+  </si>
+  <si>
+    <t>MIDTOWN NAIL LOUNGE</t>
+  </si>
+  <si>
+    <t>Asana Nail Salon</t>
+  </si>
+  <si>
+    <t>Nails Bar Of American</t>
+  </si>
+  <si>
+    <t>16th St Nails &amp; Spa</t>
+  </si>
+  <si>
+    <t>Luxury Nails &amp; Spa($20.000 CASH WINNERS START SOON)</t>
+  </si>
+  <si>
+    <t>5th Avenue Nail Bar</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Jolly+Nails+%26+Spa/data=!4m7!3m6!1s0x865cf7937263d961:0xa20ca61398ab5b98!8m2!3d29.3511225!4d-98.4597993!16s%2Fg%2F11dfwyh53b!19sChIJYdljcpP3XIYRmFurmBOmDKI?authuser=0&amp;hl=en&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Karinas+nails/data=!4m2!3m1!1s0x0:0x7c87d75cec3e2831?sa=X&amp;ved=1t:2428&amp;ictx=111&amp;cshid=1748540879468700</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/LA+SPA+%26+NAILBAR/data=!4m7!3m6!1s0x89c676a409213c21:0x81340bd833d8c972!8m2!3d40.3590747!4d-75.9820956!16s%2Fg%2F1ts1nlkt!19sChIJITwhCaR2xokRcsnYM9gLNIE?authuser=0&amp;hl=en&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/ProfessioNAIL+QueensPlaza/data=!4m7!3m6!1s0x6b915a034baa1569:0x26e47a4f7b406ee!8m2!3d-27.4685928!4d153.0265488!16s%2Fg%2F11gf9fltcz!19sChIJaRWqSwNakWsR7ga096RHbgI?authuser=0&amp;hl=en&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/fcFV43ExpUSYM4kHA</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/TLC+NAILS+%26+SPA+Easley/data=!4m7!3m6!1s0x885837cea32f48c9:0x3c2a12adfda03194!8m2!3d34.8229891!4d-82.5573576!16s%2Fg%2F11ll9dgfwz!19sChIJyUgvo843WIgRlDGg_a0SKjw?authuser=0&amp;hl=en&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/VIP+Nails+and+Spa/data=!4m7!3m6!1s0x885868d4313cf273:0x60f963b8c47a50c0!8m2!3d34.5584148!4d-82.6964295!16s%2Fg%2F1tf6hbzj!19sChIJc_I8MdRoWIgRwFB6xLhj-WA?authuser=0&amp;hl=en&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Verona+Nails+%26+Spa/data=!4m7!3m6!1s0x876b7e8095d048f1:0x484a3133032a250a!8m2!3d39.5682169!4d-105.0803812!16s%2Fg%2F1260vxdjm!19sChIJ8UjQlYB-a4cRCiUqAzMxSkg?authuser=0&amp;hl=en&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Secrets+Nails+%26+Spa/data=!4m7!3m6!1s0x88d90638e325d3dd:0x8a51d020d01acd3e!8m2!3d26.1511364!4d-80.2565507!16s%2Fg%2F1thq6287!19sChIJ3dMl4zgG2YgRPs0a0CDQUYo?authuser=0&amp;hl=en&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Nailshop/data=!4m7!3m6!1s0x88f5007fd7df78e9:0x5014b5885236f03a!8m2!3d33.7079493!4d-84.2704601!16s%2Fg%2F1tg87h6n!19sChIJ6Xjf138A9YgROvA2Uoi1FFA?authuser=0&amp;hl=en&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Envogue+Nails/data=!4m7!3m6!1s0x6ad64388fffd0e4f:0xad492e3d109dd182!8m2!3d-37.812752!4d144.9641903!16s%2Fg%2F11lly6v8hs!19sChIJTw79_4hD1moRgtGdED0uSa0?authuser=0&amp;hl=en&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Vip+Nails+Baytown/data=!4m7!3m6!1s0x863f5c1dfb7186ef:0xc54e158b80021823!8m2!3d29.7712294!4d-94.9761262!16s%2Fg%2F11c602l5mq!19sChIJ74Zx-x1cP4YRIxgCgIsVTsU?authuser=0&amp;hl=en&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/LUX+Nails+%26+Lashes/data=!4m7!3m6!1s0x876c7d5f94188639:0x2832e926a3bb64d4!8m2!3d39.6742416!4d-104.8672196!16s%2Fg%2F11clsy1syg!19sChIJOYYYlF99bIcR1GS7oybpMig?authuser=0&amp;hl=en&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Bedazzled+nails+and+bar/data=!4m7!3m6!1s0x876c9113ff197db3:0x79351df90aafd84a!8m2!3d39.4938187!4d-104.7596613!16s%2Fg%2F11kk0rbn96!19sChIJs30Z_xORbIcRStivCvkdNXk?authuser=0&amp;hl=en&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/GLORY+NAILS+%26+BEAUTY+II/data=!4m7!3m6!1s0x6ad642cad30f0cd7:0x8a73b35a48361f87!8m2!3d-37.8100517!4d144.9610232!16s%2Fg%2F11c2q_0tck!19sChIJ1wwP08pC1moRhx82SFqzc4o?authuser=0&amp;hl=en&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Jolly+Nails+%26+Spa/@29.3511225,-98.4597993,17z/data=!3m1!4b1!4m6!3m5!1s0x865cf7937263d961:0xa20ca61398ab5b98!8m2!3d29.3511225!4d-98.4597993!16s%2Fg%2F11dfwyh53b?authuser=0&amp;hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI1MDUyOC4wIKXMDSoASAFQAw%3D%3D</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Prince+Beauty+Supply/data=!4m7!3m6!1s0x87df35699f9c8a69:0x954af71b360257f6!8m2!3d38.6762314!4d-90.3122206!16s%2Fg%2F1tctg4my!19sChIJaYqcn2k134cR9lcCNhv3SpU?authuser=0&amp;hl=en&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Fontainebleau+Nail+Salon+%26+Spa/data=!4m7!3m6!1s0x864eab03530ab401:0x4b366983942c4482!8m2!3d32.8924215!4d-96.4704576!16s%2Fg%2F11thqwwc63!19sChIJAbQKUwOrToYRgkQslINpNks?authuser=0&amp;hl=en&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Maruti+Eyebrow+Threading+and+Lashes/data=!4m7!3m6!1s0x88626f1c5c2e8fa9:0x9187f4a89e31c546!8m2!3d34.7014212!4d-86.5846405!16s%2Fg%2F11g4hv381d!19sChIJqY8uXBxvYogRRsUxnqj0h5E?authuser=0&amp;hl=en&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/LUXURY+NAIL+BAR+%2820%25+OFF+SECONDS+SERVICE+FOR+NEW+CUSTOMERS%29+Monday+to+Wednesday.+Please+let+Counter+know!/data=!4m7!3m6!1s0x864e215df2fad2cb:0xc0be6c3c06d35d1f!8m2!3d32.4388847!4d-97.7660446!16s%2Fg%2F11fvcll_cn!19sChIJy9L68l0hToYRH13TBjxsvsA?authuser=0&amp;hl=en&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Danah+beauty%26spa,beauty+center,saloon/@31.9778171,35.8440452,17z/data=!3m1!4b1!4m6!3m5!1s0x151b5fb85d7981af:0x6ad59da137631903!8m2!3d31.9778171!4d35.8440452!16s%2Fg%2F12hqgb24l?authuser=0&amp;hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI1MDYxNi4wIKXMDSoASAFQAw%3D%3D</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Saige+Boutique+and+Salon/data=!4m7!3m6!1s0x88310269db61f755:0x7e0fce70c5afc8ce!8m2!3d41.4981069!4d-81.495076!16s%2Fg%2F11bxnq_3ht!19sChIJVfdh22kCMYgRzsivxXDOD34?authuser=0&amp;hl=en&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Nails+%26+Spa+Salon+Midtown,+NYC/data=!4m7!3m6!1s0x89c259c7b2686727:0xca664bbbcd7b6711!8m2!3d40.762288!4d-73.9768915!16s%2Fg%2F11s5p0r5f1!19sChIJJ2dossdZwokREWd7zbtLZso?authuser=0&amp;hl=en&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Nail+Talk+%26+Tan/data=!4m7!3m6!1s0x88f509596c241e3b:0x368351f2686126ff!8m2!3d33.9298427!4d-84.3401795!16s%2Fg%2F1tjh06bv!19sChIJOx4kbFkJ9YgR_yZhaPJRgzY?authuser=0&amp;hl=en&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Vienna+Nail+And+lashes/@37.2492971,-121.8318212,17z/data=!3m1!4b1!4m6!3m5!1s0x808e31ed759f092f:0xa49970b1e87d808c!8m2!3d37.2492971!4d-121.8318212!16s%2Fg%2F1tdkb97j?authuser=0&amp;hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI1MDUyOC4wIKXMDSoASAFQAw%3D%3D</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Hollywood+spa+%26+nails/data=!4m7!3m6!1s0x88773d2012b2d849:0x5515cf97936f007c!8m2!3d37.7928351!4d-89.0285162!16s%2Fg%2F11hdl37_zy!19sChIJSdiyEiA9d4gRfABvk5fPFVU?authuser=0&amp;hl=en&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Eric+%26+Mia+Nails+Spa+%2810%25+OFF+New+customers%29/data=!4m7!3m6!1s0x8713499a5b0a6ea5:0xa8866b6bf0affd13!8m2!3d38.8863166!4d-104.7163471!16s%2Fg%2F11h5rpk5jv!19sChIJpW4KW5pJE4cRE_2v8Gtrhqg?authuser=0&amp;hl=en&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/The+White+Spa+Nails/data=!4m7!3m6!1s0x872baf21e8681b05:0x3de38a19f3913000!8m2!3d33.381894!4d-111.7384228!16s%2Fg%2F11bw3c_19h!19sChIJBRto6CGvK4cRADCR8xmK4z0?authuser=0&amp;hl=en&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/360+Nails+%26+Spa/data=!4m7!3m6!1s0x876c766f0afe29bb:0xd532fa7c97a3562b!8m2!3d39.883938!4d-104.9977136!16s%2Fg%2F11dxrskq6n!19sChIJuyn-Cm92bIcRK1ajl3z6MtU?authuser=0&amp;hl=en&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/PALACE+NAIL+LOUNGE+-+MESA/data=!4m7!3m6!1s0x872b09a29a1ef237:0xfeacca648371eed3!8m2!3d33.4299358!4d-111.8734717!16s%2Fg%2F11fj5hv08b!19sChIJN_IemqIJK4cR0-5xg2TKrP4?authuser=0&amp;hl=en&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Manhattan+Beauty+Supply/data=!4m7!3m6!1s0x89ba9733b5a7ea5d:0x98739390f7fd4f0b!8m2!3d36.9154863!4d-76.239414!16s%2Fg%2F1v6qjj63!19sChIJXeqntTOXuokRC0_995CTc5g?authuser=0&amp;hl=en&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Le+Passion+Nails+%26+Spa/data=!4m7!3m6!1s0x872b15e4f0d90d41:0x8df53f34919aed62!8m2!3d33.4208431!4d-112.2245607!16s%2Fg%2F1w665wm8!19sChIJQQ3Z8OQVK4cRYu2akTQ_9Y0?authuser=0&amp;hl=en&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Vuvuzela+Nail+Spa/data=!4m7!3m6!1s0x8640d95e4e311e97:0x6eb464ab414e7871!8m2!3d29.7893674!4d-95.6888871!16s%2Fg%2F11f9v2xwcy!19sChIJlx4xTl7ZQIYRcXhOQatktG4?authuser=0&amp;hl=en&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Joe+Nails+Salon+Round+Rock+Austin+Texas/@30.4891528,-97.7299607,17z/data=!3m1!4b1!4m6!3m5!1s0x8644d2775a8a35a3:0xf362e61567a0b1b5!8m2!3d30.4891528!4d-97.7299607!16s%2Fg%2F1td0yw6r?authuser=0&amp;hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI1MDUyOC4wIKXMDSoASAFQAw%3D%3D</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Anna+Nail+and+Spa/data=!4m7!3m6!1s0x884087cb4541a9c1:0xd22b6a529ff51f4!8m2!3d39.6837553!4d-84.2214989!16s%2Fg%2F11g04v255x!19sChIJwalBRcuHQIgR9FH_KaW2Ig0?authuser=0&amp;hl=en&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Professional+Nails+%26+spa+LLC/data=!4m7!3m6!1s0x888e8561cf229e61:0x58cd5c08226249e4!8m2!3d32.4628455!4d-86.4149936!16s%2Fg%2F1tdjxsvs!19sChIJYZ4iz2GFjogR5EliIghczVg?authuser=0&amp;hl=en&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/D%E2%80%99or+Nail+Bar+%26+Lash+Atlanta/data=!4m7!3m6!1s0x88f5012d18cd4581:0x6586aa7e1c816ad4!8m2!3d33.7564399!4d-84.3487315!16s%2Fg%2F11s0tf7ps6!19sChIJgUXNGC0B9YgR1GqBHH6qhmU?authuser=0&amp;hl=en&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Tomato+Nails+Salon+Inc/data=!4m7!3m6!1s0x89c24db679ba8713:0x65426a5182df5a5a!8m2!3d40.6254108!4d-74.1497094!16s%2Fg%2F1ts3m37t!19sChIJE4e6ebZNwokRWlrfglFqQmU?authuser=0&amp;hl=en&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/NAILS+OF+AMERICA+LOOP+336+CONROE/data=!4m7!3m6!1s0x8647391af624c29f:0xdf927ffa2d3c62c8!8m2!3d30.2784063!4d-95.4658429!16s%2Fg%2F11ffv2wsyx!19sChIJn8Ik9ho5R4YRyGI8Lfp_kt8?authuser=0&amp;hl=en&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Legacy+Nail+Salon/data=!4m7!3m6!1s0x865c8a1e1ee2cc41:0xe1467a3e73dba6a9!8m2!3d29.6110236!4d-98.4668071!16s%2Fg%2F1tjyv0mk!19sChIJQcziHh6KXIYRqabbcz56RuE?authuser=0&amp;hl=en&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Magic+Nails+%26+Tanning/data=!4m7!3m6!1s0x87dec879ba0bf1e5:0xb8cab4b234abe1ef!8m2!3d38.8148498!4d-90.874207!16s%2Fg%2F1tf60v6v!19sChIJ5fELunnI3ocR7-GrNLK0yrg?authuser=0&amp;hl=en&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Senorita+nail+%26+spa/data=!4m7!3m6!1s0x54843fece0bfa369:0xb0e8dade536cfe3c!8m2!3d49.1597111!4d-121.953243!16s%2Fg%2F11v009w_1t!19sChIJaaO_4Ow_hFQRPP5sU97a6LA?authuser=0&amp;hl=en&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/MV+Nail+Bar+and+Spa/data=!4m7!3m6!1s0x8869718977bde17f:0x11034599bd84ff!8m2!3d38.3353025!4d-85.7075879!16s%2Fg%2F11tmzg18d7!19sChIJf-G9d4lxaYgR_4S9mUUDEQA?authuser=0&amp;hl=en&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Super+Nail/data=!4m7!3m6!1s0x86d671deb105b915:0x81984e750dc4abfb!8m2!3d32.250005!4d-110.9079433!16s%2Fg%2F1tdb03qp!19sChIJFbkFsd5x1oYR-6vEDXVOmIE?authuser=0&amp;hl=en&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Morii+Nails+Spa/data=!4m7!3m6!1s0x880efbb9a92ad993:0x23e5282541278772!8m2!3d41.8168295!4d-88.2788577!16s%2Fg%2F11splfymx1!19sChIJk9kqqbn7DogRcocnQSUo5SM?authuser=0&amp;hl=en&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Best+Beauty+Nail+Salon/data=!4m7!3m6!1s0x80c8c0a8bed59b75:0x91b75f9b66615b90!8m2!3d36.161805!4d-115.2872775!16s%2Fg%2F1vzn5vcm!19sChIJdZvVvqjAyIARkFthZptft5E?authuser=0&amp;hl=en&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/UPSCALE+NAILS+%26+SPA+%7C+BEST+NAIL+DESIGNS+IN+STL+%7C+PERMANENT+JEWELRY/data=!4m7!3m6!1s0x87d8c7fe84055555:0x642efa7a712ab2a2!8m2!3d38.4814605!4d-90.3039855!16s%2Fg%2F11ggnjvv8k!19sChIJVVUFhP7H2IcRorIqcXr6LmQ?authuser=0&amp;hl=en&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Jenny%27s+Nails+On+The+Drive/data=!4m7!3m6!1s0x54867148a0484983:0x2452d09c30b9f297!8m2!3d49.2655129!4d-123.0698979!16s%2Fg%2F11b61p_hbs!19sChIJg0lIoEhxhlQRl_K5MJzQUiQ?authuser=0&amp;hl=en&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/A+Q+Nails/data=!4m7!3m6!1s0x89b65d1df1fde2ab:0x59a23e467642fc1c!8m2!3d38.7886313!4d-77.5169494!16s%2Fg%2F1pt_gsf9_!19sChIJq-L98R1dtokRHPxCdkY-olk?authuser=0&amp;hl=en&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Nails+of+America+Baytown/data=!4m7!3m6!1s0x863f59541c2ee8d5:0xd3806749c72cde6b!8m2!3d29.7931189!4d-94.9827722!16s%2Fg%2F11c2mdcqlj!19sChIJ1eguHFRZP4YRa94sx0lngNM?authuser=0&amp;hl=en&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Casa+Blanca+Nail+Bar/data=!4m7!3m6!1s0x88541d474e579281:0x95e6f9acccae2ea2!8m2!3d35.3744068!4d-80.7879096!16s%2Fg%2F11f3ggsl7g!19sChIJgZJXTkcdVIgRoi6uzKz55pU?authuser=0&amp;hl=en&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/DREAM+NAIL+SPA-Tidwell+Rd,77044/data=!4m7!3m6!1s0x8640a5e5c234fceb:0x12ee62559d740165!8m2!3d29.8538608!4d-95.1888275!16s%2Fg%2F11q94_3s_s!19sChIJ6_w0wuWlQIYRZQF0nVVi7hI?authuser=0&amp;hl=en&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/A%2B+Nail+Spa/data=!4m7!3m6!1s0x89c267314aac73f5:0x825244dab3a6b064!8m2!3d40.686923!4d-73.823059!16s%2Fg%2F11svvgrhfj!19sChIJ9XOsSjFnwokRZLCms9pEUoI?authuser=0&amp;hl=en&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/LUSH+NAIL+BAR+DUNWOODY+%28NEXT+TO+ONELIFE+FITNESS%2F+OLD+NAVY%2F+MARSHALL%29/data=!4m7!3m6!1s0x88f5095fea1f6453:0x2d64f0ee156d1159!8m2!3d33.9196344!4d-84.3420241!16s%2Fg%2F11k443lrhr!19sChIJU2Qf6l8J9YgRWRFtFe7wZC0?authuser=0&amp;hl=en&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Lisa%27s+Nails+And+Spas/data=!4m7!3m6!1s0x80945edff93b03e3:0xfb6b2f7658ae8211!8m2!3d36.7363262!4d-119.7192812!16s%2Fg%2F1pwftq_ls!19sChIJ4wM7-d9elIAREYKuWHYva_s?authuser=0&amp;hl=en&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Q-Nails+Summerwood/data=!4m7!3m6!1s0x53a03d9564bf78ef:0x8e50fbe19f5d2296!8m2!3d53.5568874!4d-113.274226!16s%2Fg%2F1tp_61ss!19sChIJ73i_ZJU9oFMRliJdn-H7UI4?authuser=0&amp;hl=en&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Nails+Escape/data=!4m7!3m6!1s0x8874b268dcb00001:0x62a46c8ade764622!8m2!3d39.9232408!4d-88.9566791!16s%2Fg%2F11gglrtndn!19sChIJAQCw3GiydIgRIkZ23opspGI?authuser=0&amp;hl=en&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/LaBelle+Spa+%26+Nails/data=!4m7!3m6!1s0x89c0e52ad0d9530d:0x3abb04c903160d0a!8m2!3d39.472869!4d-74.4599701!16s%2Fg%2F11s0z9dzqj!19sChIJDVPZ0CrlwIkRCg0WA8kEuzo?authuser=0&amp;hl=en&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Layla%27s+Day+Spa+30%25+OFF+2nd+SERVICES/data=!4m7!3m6!1s0x864ea594bf6555b9:0xc49c469a8ef9aff9!8m2!3d32.7917244!4d-96.5953554!16s%2Fg%2F1wnbyf5y!19sChIJuVVlv5SlToYR-a_5jppGnMQ?authuser=0&amp;hl=en&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Q%27s+Nails+2/data=!4m7!3m6!1s0x89b7c1cff8c00fb1:0xd9a8528b133a9945!8m2!3d38.9590239!4d-76.8686729!16s%2Fg%2F11kg00t52x!19sChIJsQ_A-M_Bt4kRRZk6E4tSqNk?authuser=0&amp;hl=en&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Layla%27s+Day+Spa+%2820%25+OFF+NEW+MANAGEMENT%29/data=!4m7!3m6!1s0x864ea594bf6555b9:0xc49c469a8ef9aff9!8m2!3d32.7917244!4d-96.5953554!16s%2Fg%2F1wnbyf5y!19sChIJuVVlv5SlToYR-a_5jppGnMQ?authuser=0&amp;hl=en&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Edana+Beauty+%28+Nail+bar+%26+massage+%29/data=!4m7!3m6!1s0x6b915b84da750f93:0xc00bd184eb66d8ec!8m2!3d-27.4695568!4d153.0223999!16s%2Fg%2F11j0qwq6zg!19sChIJkw912oRbkWsR7Nhm64TRC8A?authuser=0&amp;hl=en&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Omega+Nails/data=!4m7!3m6!1s0x88f459d837ccbb73:0xea6faaa4bfda7861!8m2!3d33.4653947!4d-84.2241738!16s%2Fg%2F11vypcctbc!19sChIJc7vMN9hZ9IgRYXjav6Sqb-o?authuser=0&amp;hl=en&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/M+%26+M+nails+and+Spa/data=!4m7!3m6!1s0x884609c59f06686f:0xd241c54cb677bb1!8m2!3d38.4223611!4d-82.4438414!16s%2Fg%2F11cs1sbclh!19sChIJb2gGn8UJRogRsXtny1QcJA0?authuser=0&amp;hl=en&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/West+Bend+Nails/data=!4m7!3m6!1s0x88045fce149af55f:0x24adf6309c68097e!8m2!3d43.3969462!4d-88.1936619!16s%2Fg%2F11v0ffy3pq!19sChIJX_WaFM5fBIgRfglonDD2rSQ?authuser=0&amp;hl=en&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Trina+Nails+Of+The+World/data=!4m7!3m6!1s0x872ba83d6f698037:0x2662b6802258f678!8m2!3d33.3802919!4d-111.842813!16s%2Fg%2F1tmcmq3g!19sChIJN4Bpbz2oK4cRePZYIoC2YiY?authuser=0&amp;hl=en&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Hector+Nails/data=!4m7!3m6!1s0x865cf7174b275d3b:0xf48b414fbc3452df!8m2!3d29.350988!4d-98.4320051!16s%2Fg%2F11f6589kpm!19sChIJO10nSxf3XIYR31I0vE9Bi_Q?authuser=0&amp;hl=en&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/T+and+D+Nail+Salon/data=!4m7!3m6!1s0x88c2dd243f1c3561:0xd20ceb105cd1bdea!8m2!3d27.8937505!4d-82.5251909!16s%2Fg%2F11hbh5hmt3!19sChIJYTUcPyTdwogR6r3RXBDrDNI?authuser=0&amp;hl=en&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Jana+Nails+and+Spa/data=!4m7!3m6!1s0x54856db9affee0bb:0xe6613f5ab73c509f!8m2!3d48.4650955!4d-122.3353118!16s%2Fg%2F11bbrhzll7!19sChIJu-D-r7lthVQRn1A8t1o_YeY?authuser=0&amp;hl=en&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Viva+Nails,+Hair+%26+Spa/data=!4m7!3m6!1s0x89c14cd4f8a603b5:0xb2d633af9113733d!8m2!3d40.088833!4d-74.965986!16s%2Fg%2F1th1dml_!19sChIJtQOm-NRMwYkRPXMTka8z1rI?authuser=0&amp;hl=en&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Lacey+Nails/data=!4m7!3m6!1s0x5491733eeb9e501b:0xfd5df0df90d339f1!8m2!3d46.9975881!4d-122.8200667!16s%2Fg%2F1tfxgd2s!19sChIJG1Ce6z5zkVQR8TnTkN_wXf0?authuser=0&amp;hl=en&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/K-Nails+%26+Spa/data=!4m7!3m6!1s0x535b07831c6be6cf:0x49c4f6a376d60328!8m2!3d45.9695739!4d-112.5090408!16s%2Fg%2F11q_5vf1jr!19sChIJz-ZrHIMHW1MRKAPWdqP2xEk?authuser=0&amp;hl=en&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Rico+Nails/data=!4m7!3m6!1s0x88f5105136500289:0x168d0f1b1131d65f!8m2!3d33.88884!4d-84.475283!16s%2Fg%2F1w97w6p7!19sChIJiQJQNlEQ9YgRX9YxERsPjRY?authuser=0&amp;hl=en&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/XO+Beauty+Nails+and+Hair/data=!4m7!3m6!1s0x54950f20141ca56f:0xc8c5c85c6e8681d!8m2!3d45.5173787!4d-122.8427944!16s%2Fg%2F11cks1dsrt!19sChIJb6UcFCAPlVQRHWjoxoVcjAw?authuser=0&amp;hl=en&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Caribbean+Nails+%26+Spa+84045/data=!4m7!3m6!1s0x874d7f5f4ba63f1b:0x3758ffe94d3e5ec4!8m2!3d40.38813!4d-111.9112146!16s%2Fg%2F11q85zsppg!19sChIJGz-mS19_TYcRxF4-Ten_WDc?authuser=0&amp;hl=en&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Luminous+V+Nail+Spa+-+Springboro/data=!4m7!3m6!1s0x88408b737be83a13:0x5be57786800adefc!8m2!3d39.5574226!4d-84.2342147!16s%2Fg%2F11rfcbj_8k!19sChIJEzroe3OLQIgR_N4KgIZ35Vs?authuser=0&amp;hl=en&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Hot+Tips+Nail+Lounge+A1+of+Rockaway/data=!4m7!3m6!1s0x89c30a2315480ab7:0x38bbe1580e4b5ced!8m2!3d40.891513!4d-74.5096211!16s%2Fg%2F11cm15x87t!19sChIJtwpIFSMKw4kR7VxLDljhuzg?authuser=0&amp;hl=en&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/ATNL+Nails+-+Spa+%26+Beauty/data=!4m7!3m6!1s0x6b164daed9707609:0xa725c86915d51b40!8m2!3d-35.276068!4d149.1340386!16s%2Fg%2F11j8rj8csf!19sChIJCXZw2a5NFmsRQBvVFWnIJac?authuser=0&amp;hl=en&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/LA+Nails+in+Lititz+PA/data=!4m7!3m6!1s0x89c62291ef1227b1:0x446c4f7a527522e3!8m2!3d40.129787!4d-76.308342!16s%2Fg%2F1tdlcn_v!19sChIJsScS75EixokR4yJ1UnpPbEQ?authuser=0&amp;hl=en&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Ooh+La+La+Salon+%26+Spa/data=!4m7!3m6!1s0x887d37d8e9df1919:0x2e5bd34b5893253d!8m2!3d34.8420506!4d-87.6716666!16s%2Fg%2F11fy9g8nhr!19sChIJGRnf6dg3fYgRPSWTWEvTWy4?authuser=0&amp;hl=en&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Top+Prestige+Nails/data=!4m7!3m6!1s0x883b5257076ff825:0x5d4f5c6b015dc65a!8m2!3d42.3239733!4d-83.4572902!16s%2Fg%2F1tdpsb8l!19sChIJJfhvB1dSO4gRWsZdAWtcT10?authuser=0&amp;hl=en&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/K1+Nails+%26+Spa/data=!4m7!3m6!1s0x876ea129cc84f1c9:0x78798b409514fa46!8m2!3d40.4035842!4d-104.7333903!16s%2Fg%2F11g0mkqwmb!19sChIJyfGEzCmhbocRRvoUlUCLeXg?authuser=0&amp;hl=en&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Craze+Nails+%26+Spa+in+Lake+Mary/data=!4m7!3m6!1s0x88e76d48e521cfb7:0x1cddb6c0051f94e2!8m2!3d28.7577847!4d-81.3214564!16s%2Fg%2F11bzz0tb6b!19sChIJt88h5Uht54gR4pQfBcC23Rw?authuser=0&amp;hl=en&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Splendid+Nail+Bar/data=!4m7!3m6!1s0x885408d5cfe66bed:0xf24d96a745f238ba!8m2!3d35.4643713!4d-80.5931329!16s%2Fg%2F1vn196yl!19sChIJ7Wvmz9UIVIgRujjyRaeWTfI?authuser=0&amp;hl=en&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Sara%E2%80%99s+Wax+%26+Beauty+Bar/data=!4m7!3m6!1s0x88d9b904ffffffff:0x48716f09430c04b!8m2!3d25.7633066!4d-80.3062522!16s%2Fg%2F11hc_k6wqt!19sChIJ_____wS52YgRS8AwlPAWhwQ?authuser=0&amp;hl=en&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Key+West+Nail+Lounge/data=!4m7!3m6!1s0x88d1b6cca062c649:0x8f2f0c868868068c!8m2!3d24.562942!4d-81.7751988!16s%2Fg%2F11f3h5w79b!19sChIJScZioMy20YgRjAZoiIYML48?authuser=0&amp;hl=en&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Katie%27s+Nails+%26+Spa/data=!4m7!3m6!1s0x88e711033a502815:0x49775f3f7917f6b3!8m2!3d28.9015884!4d-81.2863006!16s%2Fg%2F11b6njqrgj!19sChIJFShQOgMR54gRs_YXeT9fd0k?authuser=0&amp;hl=en&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/CH%C3%8DC+NAIL+LOUNGE+BIGFORK/data=!4m7!3m6!1s0x5367b3d6fb5c138d:0x2f87bbf3f6b61d67!8m2!3d48.0774955!4d-114.0782012!16s%2Fg%2F11q4l0pxpm!19sChIJjRNc-9azZ1MRZx229vO7hy8?authuser=0&amp;hl=en&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Images+Face+%26+Body+Clinic/data=!4m7!3m6!1s0x4888761e0ede5d75:0xfa65824c142ae175!8m2!3d55.8993506!4d-3.6399087!16s%2Fg%2F1tfzx1vv!19sChIJdV3eDh52iEgRdeEqFEyCZfo?authuser=0&amp;hl=en&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Best+Nail+Lounge+%28+ShopRite+Plaza+On+Lincoln+%26+East+Landis+Ave+%29/data=!4m7!3m6!1s0x89c0cd50b62a088d:0xb5d3bec3a620ae46!8m2!3d39.4843523!4d-74.9577868!16s%2Fg%2F1tlbvm6h!19sChIJjQgqtlDNwIkRRq4gpsO-07U?authuser=0&amp;hl=en&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Wooster+Nail+Spa/data=!4m7!3m6!1s0x88374915c7978443:0xa480f4126ecfc380!8m2!3d40.8484997!4d-81.9430514!16s%2Fg%2F11k2b21r8h!19sChIJQ4SXxxVJN4gRgMPPbhL0gKQ?authuser=0&amp;hl=en&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Tommy+Nails/data=!4m7!3m6!1s0x89daef81866ec517:0x3c7a38fbd8d3ac!8m2!3d42.1073236!4d-75.9073948!16s%2Fg%2F1tk68p1_!19sChIJF8VuhoHv2okRrNPY-zh6PAA?authuser=0&amp;hl=en&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/West+U+Nails+%26+Facial/data=!4m7!3m6!1s0x8640c1b41b19f031:0x83c3236515c13d84!8m2!3d29.7054117!4d-95.4406103!16s%2Fg%2F1tm1qvt4!19sChIJMfAZG7TBQIYRhD3BFWUjw4M?authuser=0&amp;hl=en&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Millenia+Nails+%26+Day+Spa/data=!4m7!3m6!1s0x89ab135a94dfd031:0xf95c6b7d3e251f00!8m2!3d35.045051!4d-78.919109!16s%2Fg%2F1thq64h0!19sChIJMdDflFoTq4kRAB8lPn1rXPk?authuser=0&amp;hl=en&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Fancy+Nail/data=!4m7!3m6!1s0x54ae4ca5a6e63797:0x8a1f1030140cbe06!8m2!3d43.6091172!4d-116.6062823!16s%2Fg%2F1tdn3tlf!19sChIJlzfmpqVMrlQRBr4MFDAQH4o?authuser=0&amp;hl=en&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Five+Star+Nail+Salon/data=!4m7!3m6!1s0x88dd871515834645:0xe2938d4d1fa5b7fd!8m2!3d28.3768667!4d-81.4029778!16s%2Fg%2F1tz76svn!19sChIJRUaDFRWH3YgR_belH02Nk-I?authuser=0&amp;hl=en&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Midtown+Centre+Oriental+Nails/data=!4m7!3m6!1s0x8811c260b7619cad:0xf5d8939e9ececa3e!8m2!3d41.5892064!4d-87.3379164!16s%2Fg%2F1thd2dh4!19sChIJrZxht2DCEYgRPsrOnp6T2PU?authuser=0&amp;hl=en&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Vy%27s+Nail+Spa/data=!4m7!3m6!1s0x89ba9838e733f609:0x1b1bd184450d3f!8m2!3d36.8683601!4d-76.2912699!16s%2Fg%2F1tjbt1r9!19sChIJCfYz5ziYuokRPw1FhNEbGwA?authuser=0&amp;hl=en&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Magic+Nails+of+Lemont/data=!4m7!3m6!1s0x880e435270db571b:0xd0785b64a0af25c5!8m2!3d41.6601445!4d-88.0013999!16s%2Fg%2F11j31vppch!19sChIJG1fbcFJDDogRxSWvoGRbeNA?authuser=0&amp;hl=en&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Blissful+Nail+Lounge/data=!4m7!3m6!1s0x89ac470214ba23f5:0x9b434663c09b5571!8m2!3d35.82148!4d-78.3259461!16s%2Fg%2F11vd8w_t0y!19sChIJ9SO6FAJHrIkRcVWbwGNGQ5s?authuser=0&amp;hl=en&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Jasmine+Nails+Puyallup/data=!4m7!3m6!1s0x5490fcfedeb58d57:0xb9b78bf1cc158b78!8m2!3d47.143407!4d-122.2923946!16s%2Fg%2F1tdkrht_!19sChIJV4213v78kFQReIsVzPGLt7k?authuser=0&amp;hl=en&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Plano+Nail+Bar/data=!4m7!3m6!1s0x864c1865a55848e9:0xc76f237521c12af3!8m2!3d33.0432325!4d-96.7338388!16s%2Fg%2F11b7qsyqxk!19sChIJ6UhYpWUYTIYR8yrBIXUjb8c?authuser=0&amp;hl=en&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/RUBY%E2%80%99S+NAILS+SALON/data=!4m7!3m6!1s0x54905b4991a4544d:0x627f2c7a19f38b0!8m2!3d47.3682013!4d-122.3037402!16s%2Fg%2F11sbb3y2hm!19sChIJTVSkkUlbkFQRsDifocfyJwY?authuser=0&amp;hl=en&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Lux+Nail+Spa+%26+Hair+Salon/data=!4m7!3m6!1s0x89c8051d870afa69:0xc2d12b4aae72e0ab!8m2!3d39.3282045!4d-76.6098157!16s%2Fg%2F1tffvxdv!19sChIJafoKhx0FyIkRq-Byrkor0cI?authuser=0&amp;hl=en&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Galaxy+Nail+Lounge/data=!4m7!3m6!1s0x8854b5d7e3508c3d:0xa1b2851054d67087!8m2!3d35.1658134!4d-79.4051895!16s%2Fg%2F11g_vdb6y8!19sChIJPYxQ49e1VIgRh3DWVBCFsqE?authuser=0&amp;hl=en&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Urbane+Nails+%26+Spa+2/data=!4m7!3m6!1s0x87b21c727c6d3ebf:0xf9e7abe8c0a7a486!8m2!3d35.6022911!4d-97.5486602!16s%2Fg%2F11f3n8n5nn!19sChIJvz5tfHIcsocRhqSnwOir5_k?authuser=0&amp;hl=en&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Talk+Nail+%26+Spa/data=!4m7!3m6!1s0x872b152fef56b085:0xc1f84a8ad39d87ae!8m2!3d33.49526!4d-112.2017797!16s%2Fg%2F1tvym750!19sChIJhbBW7y8VK4cRroed04pK-ME?authuser=0&amp;hl=en&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/3+sis+nail/data=!4m7!3m6!1s0x88d9ad1f28bf026f:0xdbe14af96a1b016c!8m2!3d25.9345249!4d-80.1228343!16s%2Fg%2F1260n1ypp!19sChIJbwK_KB-t2YgRbAEbavlK4ds?authuser=0&amp;hl=en&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Avi+Nail+Spa+Lash+%26+Brow/data=!4m7!3m6!1s0x88e5b03b95b19b47:0x80bf9932492654ad!8m2!3d30.4286669!4d-81.6641872!16s%2Fg%2F1tfb7cqx!19sChIJR5uxlTuw5YgRrVQmSTKZv4A?authuser=0&amp;hl=en&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/MIDTOWN+NAIL+LOUNGE/data=!4m7!3m6!1s0x872b134d391dbfc1:0xe399c7aef08be251!8m2!3d33.4872347!4d-112.0843818!16s%2Fg%2F11fcvbp441!19sChIJwb8dOU0TK4cRUeKL8K7HmeM?authuser=0&amp;hl=en&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Asana+Nail+Salon/data=!4m7!3m6!1s0x872b6de6becf07ed:0x1963bc0f1a33d193!8m2!3d33.6091956!4d-112.0668285!16s%2Fg%2F11gcz3hh99!19sChIJ7QfPvuZtK4cRk9EzGg-8Yxk?authuser=0&amp;hl=en&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Nails+Bar+Of+American/data=!4m7!3m6!1s0x86412bdc8a536013:0xf0bfafbef0ac0934!8m2!3d29.9943473!4d-95.754138!16s%2Fg%2F11rmv5n5j7!19sChIJE2BTitwrQYYRNAms8L6vv_A?authuser=0&amp;hl=en&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/16th+St+Nails+%26+Spa/data=!4m7!3m6!1s0x872b0d4d980cf7bd:0x433dfca3264a67b9!8m2!3d33.4936893!4d-112.0461863!16s%2Fg%2F11gnrs4r04!19sChIJvfcMmE0NK4cRuWdKJqP8PUM?authuser=0&amp;hl=en&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Luxury+Nails+%26+Spa%28$20.000+CASH+WINNERS+START+SOON%29/data=!4m7!3m6!1s0x875a61e31430f3d5:0x202a31fd8dabdfc3!8m2!3d41.575066!4d-109.2381592!16s%2Fg%2F11t80z875s!19sChIJ1fMwFONhWocRw9-rjf0xKiA?authuser=0&amp;hl=en&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/5th+Avenue+Nail+Bar/data=!4m7!3m6!1s0x8f4e42dd7f69b2f3:0x646ca29bf8b5e576!8m2!3d20.6490273!4d-87.0821774!16s%2Fg%2F11ddzczyyp!19sChIJ87Jpf91CTo8RduW1-JuibGQ?authuser=0&amp;hl=en&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>link_google_map</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -82,20 +730,49 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="10"/>
+      <color rgb="FF1155CC"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -103,15 +780,58 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFCCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="1">
@@ -399,82 +1119,1293 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:C116"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="38.7109375" customWidth="1"/>
+    <col min="3" max="3" width="78.5703125" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="1" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="9">
+        <v>163</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="9">
+        <v>164</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="9">
+        <v>168</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="9">
+        <v>202</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="9">
+        <v>225</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="9">
+        <v>226</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="9">
+        <v>227</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="9">
+        <v>228</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="9">
+        <v>229</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="9">
+        <v>230</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="9">
+        <v>231</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="9">
+        <v>232</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="9">
+        <v>233</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="9">
+        <v>234</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="9">
+        <v>235</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="65.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="9">
+        <v>236</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="9">
+        <v>237</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="9">
+        <v>238</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="9">
+        <v>239</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" ht="65.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="9">
+        <v>240</v>
+      </c>
+      <c r="B21" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="9">
+        <v>241</v>
+      </c>
+      <c r="B22" s="6" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>7</v>
-      </c>
-      <c r="B7" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8" t="s">
-        <v>15</v>
+      <c r="C22" s="3" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="9">
+        <v>242</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="9">
+        <v>243</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="9">
+        <v>244</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" ht="65.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="9">
+        <v>245</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="9">
+        <v>246</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="9">
+        <v>247</v>
+      </c>
+      <c r="B28" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="9">
+        <v>248</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="9">
+        <v>249</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="9">
+        <v>250</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="9">
+        <v>251</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="9">
+        <v>252</v>
+      </c>
+      <c r="B33" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="9">
+        <v>253</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" ht="78" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="9">
+        <v>254</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="9">
+        <v>255</v>
+      </c>
+      <c r="B36" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="9">
+        <v>256</v>
+      </c>
+      <c r="B37" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="9">
+        <v>257</v>
+      </c>
+      <c r="B38" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="9">
+        <v>258</v>
+      </c>
+      <c r="B39" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="9">
+        <v>259</v>
+      </c>
+      <c r="B40" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="9">
+        <v>260</v>
+      </c>
+      <c r="B41" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="9">
+        <v>261</v>
+      </c>
+      <c r="B42" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="9">
+        <v>262</v>
+      </c>
+      <c r="B43" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="9">
+        <v>263</v>
+      </c>
+      <c r="B44" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="9">
+        <v>264</v>
+      </c>
+      <c r="B45" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="9">
+        <v>265</v>
+      </c>
+      <c r="B46" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="9">
+        <v>266</v>
+      </c>
+      <c r="B47" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" ht="65.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="9">
+        <v>267</v>
+      </c>
+      <c r="B48" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="9">
+        <v>268</v>
+      </c>
+      <c r="B49" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="9">
+        <v>269</v>
+      </c>
+      <c r="B50" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="9">
+        <v>270</v>
+      </c>
+      <c r="B51" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="C51" s="3" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="9">
+        <v>271</v>
+      </c>
+      <c r="B52" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" ht="65.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="9">
+        <v>272</v>
+      </c>
+      <c r="B53" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="9">
+        <v>273</v>
+      </c>
+      <c r="B54" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="C54" s="3" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" ht="65.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="9">
+        <v>274</v>
+      </c>
+      <c r="B55" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="C55" s="3" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A56" s="9">
+        <v>275</v>
+      </c>
+      <c r="B56" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="C56" s="3" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A57" s="9">
+        <v>276</v>
+      </c>
+      <c r="B57" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="C57" s="3" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A58" s="9">
+        <v>277</v>
+      </c>
+      <c r="B58" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="C58" s="3" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A59" s="9">
+        <v>278</v>
+      </c>
+      <c r="B59" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="C59" s="3" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A60" s="9">
+        <v>279</v>
+      </c>
+      <c r="B60" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="C60" s="3" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A61" s="9">
+        <v>280</v>
+      </c>
+      <c r="B61" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="C61" s="3" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A62" s="9">
+        <v>281</v>
+      </c>
+      <c r="B62" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="C62" s="3" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A63" s="9">
+        <v>282</v>
+      </c>
+      <c r="B63" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="C63" s="3" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A64" s="9">
+        <v>283</v>
+      </c>
+      <c r="B64" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="C64" s="3" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A65" s="9">
+        <v>284</v>
+      </c>
+      <c r="B65" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="C65" s="3" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A66" s="9">
+        <v>285</v>
+      </c>
+      <c r="B66" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="C66" s="3" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A67" s="9">
+        <v>286</v>
+      </c>
+      <c r="B67" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="C67" s="3" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A68" s="9">
+        <v>287</v>
+      </c>
+      <c r="B68" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="C68" s="3" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A69" s="9">
+        <v>288</v>
+      </c>
+      <c r="B69" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="C69" s="3" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A70" s="9">
+        <v>289</v>
+      </c>
+      <c r="B70" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="C70" s="3" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A71" s="9">
+        <v>290</v>
+      </c>
+      <c r="B71" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="C71" s="3" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A72" s="9">
+        <v>291</v>
+      </c>
+      <c r="B72" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="C72" s="3" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A73" s="9">
+        <v>292</v>
+      </c>
+      <c r="B73" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="C73" s="3" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A74" s="9">
+        <v>293</v>
+      </c>
+      <c r="B74" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="C74" s="3" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A75" s="9">
+        <v>294</v>
+      </c>
+      <c r="B75" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="C75" s="3" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A76" s="9">
+        <v>295</v>
+      </c>
+      <c r="B76" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="C76" s="3" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" ht="65.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A77" s="9">
+        <v>296</v>
+      </c>
+      <c r="B77" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="C77" s="3" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A78" s="9">
+        <v>297</v>
+      </c>
+      <c r="B78" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="C78" s="3" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A79" s="9">
+        <v>298</v>
+      </c>
+      <c r="B79" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="C79" s="3" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A80" s="9">
+        <v>299</v>
+      </c>
+      <c r="B80" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="C80" s="3" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A81" s="9">
+        <v>300</v>
+      </c>
+      <c r="B81" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="C81" s="3" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A82" s="9">
+        <v>301</v>
+      </c>
+      <c r="B82" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="C82" s="3" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A83" s="9">
+        <v>302</v>
+      </c>
+      <c r="B83" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="C83" s="3" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A84" s="9">
+        <v>303</v>
+      </c>
+      <c r="B84" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="C84" s="3" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A85" s="9">
+        <v>304</v>
+      </c>
+      <c r="B85" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="C85" s="3" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A86" s="9">
+        <v>305</v>
+      </c>
+      <c r="B86" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="C86" s="3" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A87" s="9">
+        <v>306</v>
+      </c>
+      <c r="B87" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="C87" s="3" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A88" s="9">
+        <v>307</v>
+      </c>
+      <c r="B88" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="C88" s="3" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A89" s="9">
+        <v>308</v>
+      </c>
+      <c r="B89" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="C89" s="3" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A90" s="9">
+        <v>309</v>
+      </c>
+      <c r="B90" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="C90" s="3" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A91" s="9">
+        <v>310</v>
+      </c>
+      <c r="B91" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="C91" s="3" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A92" s="9">
+        <v>311</v>
+      </c>
+      <c r="B92" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="C92" s="3" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A93" s="9">
+        <v>312</v>
+      </c>
+      <c r="B93" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="C93" s="3" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A94" s="9">
+        <v>313</v>
+      </c>
+      <c r="B94" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="C94" s="3" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A95" s="9">
+        <v>314</v>
+      </c>
+      <c r="B95" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="C95" s="3" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A96" s="9">
+        <v>315</v>
+      </c>
+      <c r="B96" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="C96" s="3" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A97" s="9">
+        <v>316</v>
+      </c>
+      <c r="B97" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="C97" s="3" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A98" s="9">
+        <v>317</v>
+      </c>
+      <c r="B98" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="C98" s="3" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A99" s="9">
+        <v>318</v>
+      </c>
+      <c r="B99" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="C99" s="3" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A100" s="9">
+        <v>319</v>
+      </c>
+      <c r="B100" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="C100" s="3" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A101" s="9">
+        <v>320</v>
+      </c>
+      <c r="B101" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="C101" s="3" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A102" s="9">
+        <v>321</v>
+      </c>
+      <c r="B102" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="C102" s="3" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A103" s="9">
+        <v>322</v>
+      </c>
+      <c r="B103" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="C103" s="3" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A104" s="9">
+        <v>323</v>
+      </c>
+      <c r="B104" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="C104" s="3" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A105" s="9">
+        <v>324</v>
+      </c>
+      <c r="B105" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="C105" s="3" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A106" s="9">
+        <v>325</v>
+      </c>
+      <c r="B106" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="C106" s="3" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A107" s="9">
+        <v>326</v>
+      </c>
+      <c r="B107" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="C107" s="3" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A108" s="9">
+        <v>327</v>
+      </c>
+      <c r="B108" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="C108" s="3" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A109" s="9">
+        <v>328</v>
+      </c>
+      <c r="B109" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="C109" s="3" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A110" s="9">
+        <v>329</v>
+      </c>
+      <c r="B110" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="C110" s="3" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A111" s="9">
+        <v>330</v>
+      </c>
+      <c r="B111" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="C111" s="3" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A112" s="9">
+        <v>331</v>
+      </c>
+      <c r="B112" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="C112" s="3" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A113" s="9">
+        <v>332</v>
+      </c>
+      <c r="B113" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="C113" s="3" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A114" s="9">
+        <v>333</v>
+      </c>
+      <c r="B114" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="C114" s="3" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A115" s="9">
+        <v>334</v>
+      </c>
+      <c r="B115" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="C115" s="3" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A116" s="9">
+        <v>335</v>
+      </c>
+      <c r="B116" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="C116" s="3" t="s">
+        <v>230</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2">
-    <cfRule type="expression" dxfId="0" priority="1">
-      <formula>COUNTIF(A:A,A2)&gt;1</formula>
-    </cfRule>
-  </conditionalFormatting>
   <hyperlinks>
-    <hyperlink ref="B2" r:id="rId1"/>
+    <hyperlink ref="C2" r:id="rId1"/>
+    <hyperlink ref="C3" r:id="rId2"/>
+    <hyperlink ref="C6" r:id="rId3"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId4"/>
 </worksheet>
 </file>